--- a/raw-xlsx/119Barasat_2026_Form20.xlsx
+++ b/raw-xlsx/119Barasat_2026_Form20.xlsx
@@ -14771,7 +14771,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>Total EVM Votes</t>
+          <t>TOTAL EVM VOTES</t>
         </is>
       </c>
       <c r="B300" s="2" t="n"/>
@@ -14809,7 +14809,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>Total Postal Ballot Votes</t>
+          <t>TOTAL POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B301" s="2" t="n"/>
@@ -14847,7 +14847,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Total Votes Polled</t>
+          <t>TOTAL VOTES POLLED (GRAND TOTAL)</t>
         </is>
       </c>
       <c r="B302" s="2" t="n"/>
